--- a/Jadwal — сбор зикров.xlsx
+++ b/Jadwal — сбор зикров.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R7d8d386364fe4e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зикры" sheetId="2" r:id="R2b08bc81e3544cf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R1edc5c4a32fb42c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зикры" sheetId="2" r:id="Rf439e04b6ac74500"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -802,7 +802,7 @@
         <x:v>اللَّهُمَّ إِنِّي أَصْبَحْتُ أُشْهِدُكَ وَأُشْهِدُ حَمَلَةَ عَرْشِكَ وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَهَ إِلَّا أَنْتَ وَحْدَكَ لَا شَرِيكَ لَكَ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>Аллахумма инни асбахту (вечером: амсайту) уш-хидука ва уш-хиду хамалята 'аршик, ва маляикатак, ва джами'а халькик…</x:v>
+        <x:v>Аллахумма инни асбахту ушхиду-ка ва ушхиду хамалята ‘арши-ка ва маля’иката-ка ва джами‘а халькы-ка анна-ка анта Ллаху ля иляха илля анта вахда-ка ля шарика ля-ка ва анна Мухаммадан ‘абду-ка ва расулю-ка.</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
         <x:v>«О Аллах, я встретил утро, призывая в свидетели Тебя, носителей Твоего Трона, Твоих ангелов и всё Твоё творение, что Ты — Аллах, нет божества, кроме Тебя, и что Мухаммад — Твой раб и посланник».</x:v>
@@ -1675,7 +1675,7 @@
         <x:v>اللَّهُمَّ إِنِّي أَمْسَيْتُ أُشْهِدُكَ وَأُشْهِدُ حَمَلَةَ عَرْشِكَ وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَهَ إِلَّا أَنْتَ وَحْدَكَ لَا شَرِيكَ لَكَ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
-        <x:v>Аллахумма инни асбахту (вечером: амсайту) уш-хидука ва уш-хиду хамалята 'аршик, ва маляикатак, ва джами'а халькик…</x:v>
+        <x:v>Аллахумма инни амсайту ушхиду-ка ва ушхиду хамалята ‘арши-ка ва маля’иката-ка ва джами‘а халькы-ка анна-ка анта Ллаху ля иляха илля анта вахда-ка ля шарика ля-ка ва анна Мухаммадан ‘абду-ка ва расулю-ка.</x:v>
       </x:c>
       <x:c r="E30" s="6" t="str">
         <x:v>«О Аллах, я встретил утро, призывая в свидетели Тебя, носителей Твоего Трона, Твоих ангелов и всё Твоё творение, что Ты — Аллах, нет божества, кроме Тебя, и что Мухаммад — Твой раб и посланник».</x:v>

--- a/Jadwal — сбор зикров.xlsx
+++ b/Jadwal — сбор зикров.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R1edc5c4a32fb42c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зикры" sheetId="2" r:id="Rf439e04b6ac74500"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R41b0c8ee0c464fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зикры" sheetId="2" r:id="R709ad22a7ef24416"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1263,19 +1263,19 @@
         <x:v>«Аллаһтан басқа құдай жоқ, Ол жалғыз, серігі жоқ. Билік Оған тән, мадақ Оған, әрі Ол барлық нәрсеге құдіретті».</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>Кто скажет 100 раз в день — тому награда как за освобождение десяти рабов, записывается 100 добрых дел, стирается 100 грехов, и он под защитой от шайтана до вечера.</x:v>
+        <x:v>Кто произнесёт эти слова десять раз утром или вечером — получит награду, подобную освобождению десяти рабов; ему запишутся десять благих дел, сотрутся десять прегрешений, и он будет защищён от шайтана до вечера или до утра.</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>Кім оны күніне 100 рет айтса — он құл азат еткендей сауап алады, 100 игілік жазылады, 100 күнәсі өшіріледі, әрі кешке дейін шайтаннан қорғауда болады.</x:v>
+        <x:v>Кім бұл сөздерді таңертең немесе кешке он рет айтса, оған он құлды азат еткендей сауап жазылады, он жақсылық жазылып, он күнәсі өшіріледі әрі ол кешке дейін немесе таңға дейін шайтаннан қорғалады.</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str">
-        <x:v>ан-Насаи, ‘Амаль аль-йаум ва-ль-ляйля, 24 · Абу Дауд, 5077 · «Крепость мусульманина», № 92</x:v>
+        <x:v>ан-Насаи, ‘Амаль аль-йаум ва-ль-ляйля, 24 · «Крепость мусульманина», № 92</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="K19" s="6" t="str">
-        <x:v>«Крепость мусульманина», глава 27, № 92. Десять раз утром и вечером; при затруднении — один раз. Черновик для проверки религиозным специалистом. Сборник приложения: morning.</x:v>
+        <x:v>«Крепость мусульманина», глава 27, № 92. Десять раз утром. Иснад сахих (аль-Альбани). Вариант на 100 раз в течение дня хранится отдельно как № 93. Черновик для проверки религиозным специалистом. Сборник приложения: morning.</x:v>
       </x:c>
       <x:c r="L19" s="6" t="str">
         <x:v>черновик — религиозная проверка</x:v>
@@ -2136,19 +2136,19 @@
         <x:v>«Аллаһтан басқа құдай жоқ, Ол жалғыз, серігі жоқ. Билік Оған тән, мадақ Оған, әрі Ол барлық нәрсеге құдіретті».</x:v>
       </x:c>
       <x:c r="G42" s="9" t="str">
-        <x:v>Кто скажет 100 раз в день — тому награда как за освобождение десяти рабов, записывается 100 добрых дел, стирается 100 грехов, и он под защитой от шайтана до вечера.</x:v>
+        <x:v>Кто произнесёт эти слова десять раз утром или вечером — получит награду, подобную освобождению десяти рабов; ему запишутся десять благих дел, сотрутся десять прегрешений, и он будет защищён от шайтана до вечера или до утра.</x:v>
       </x:c>
       <x:c r="H42" s="9" t="str">
-        <x:v>Кім оны күніне 100 рет айтса — он құл азат еткендей сауап алады, 100 игілік жазылады, 100 күнәсі өшіріледі, әрі кешке дейін шайтаннан қорғауда болады.</x:v>
+        <x:v>Кім бұл сөздерді таңертең немесе кешке он рет айтса, оған он құлды азат еткендей сауап жазылады, он жақсылық жазылып, он күнәсі өшіріледі әрі ол кешке дейін немесе таңға дейін шайтаннан қорғалады.</x:v>
       </x:c>
       <x:c r="I42" s="9" t="str">
-        <x:v>ан-Насаи, ‘Амаль аль-йаум ва-ль-ляйля, 24 · Абу Дауд, 5077 · «Крепость мусульманина», № 92</x:v>
+        <x:v>ан-Насаи, ‘Амаль аль-йаум ва-ль-ляйля, 24 · «Крепость мусульманина», № 92</x:v>
       </x:c>
       <x:c r="J42" s="9" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="K42" s="9" t="str">
-        <x:v>«Крепость мусульманина», глава 27, № 92. Десять раз утром и вечером; при затруднении — один раз. Черновик для проверки религиозным специалистом. Сборник приложения: evening.</x:v>
+        <x:v>«Крепость мусульманина», глава 27, № 92. Десять раз вечером. Иснад сахих (аль-Альбани). Вариант на 100 раз в течение дня хранится отдельно как № 93. Черновик для проверки религиозным специалистом. Сборник приложения: evening.</x:v>
       </x:c>
       <x:c r="L42" s="9" t="str">
         <x:v>черновик — религиозная проверка</x:v>
